--- a/Excel2/Terminefussball_2026_HerbstV1.0.xlsx
+++ b/Excel2/Terminefussball_2026_HerbstV1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DTB\asv-neufeld\Excel2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E421A49-4BA2-4E67-BFD2-EEDD782DDB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9633941-4B63-41F9-85E3-5A3F770998E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8959,7 +8959,7 @@
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C96" s="94">
         <f>'Nach Mannschaften sortiert'!E96</f>
@@ -8997,7 +8997,7 @@
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C97" s="94">
         <f>'Nach Mannschaften sortiert'!E97</f>
@@ -9113,7 +9113,7 @@
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C100" s="94">
         <f>'Nach Mannschaften sortiert'!E100</f>
@@ -9307,7 +9307,7 @@
     </row>
     <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C105" s="94">
         <f>'Nach Mannschaften sortiert'!E105</f>
@@ -9540,7 +9540,7 @@
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C111" s="94">
         <f>'Nach Mannschaften sortiert'!E111</f>
@@ -9578,7 +9578,7 @@
     </row>
     <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C112" s="94">
         <f>'Nach Mannschaften sortiert'!E112</f>
@@ -9616,7 +9616,7 @@
     </row>
     <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C113" s="94">
         <f>'Nach Mannschaften sortiert'!E113</f>
@@ -9654,7 +9654,7 @@
     </row>
     <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C114" s="94">
         <f>'Nach Mannschaften sortiert'!E114</f>
@@ -9692,7 +9692,7 @@
     </row>
     <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C115" s="94">
         <f>'Nach Mannschaften sortiert'!E115</f>
@@ -9730,7 +9730,7 @@
     </row>
     <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C116" s="94">
         <f>'Nach Mannschaften sortiert'!E116</f>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117" s="93">
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C117" s="94">
         <f>'Nach Mannschaften sortiert'!E117</f>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="B96" s="103">
         <f>'ICS2'!B96</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C96" s="104">
         <f>'ICS2'!C96</f>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="B97" s="103">
         <f>'ICS2'!B97</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C97" s="104">
         <f>'ICS2'!C97</f>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="B100" s="103">
         <f>'ICS2'!B100</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C100" s="104">
         <f>'ICS2'!C100</f>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="B105" s="103">
         <f>'ICS2'!B105</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C105" s="104">
         <f>'ICS2'!C105</f>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="B112" s="103">
         <f>'ICS2'!B112</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C112" s="104">
         <f>'ICS2'!C112</f>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="B114" s="103">
         <f>'ICS2'!B114</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C114" s="104">
         <f>'ICS2'!C114</f>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="B115" s="103">
         <f>'ICS2'!B115</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C115" s="104">
         <f>'ICS2'!C115</f>
@@ -15867,7 +15867,7 @@
       </c>
       <c r="B116" s="103">
         <f>'ICS2'!B116</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C116" s="104">
         <f>'ICS2'!C116</f>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="B117" s="103">
         <f>'ICS2'!B117</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C117" s="104">
         <f>'ICS2'!C117</f>
@@ -16189,7 +16189,7 @@
       </c>
       <c r="B123" s="111">
         <f>'ICS2'!B113</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C123" s="112">
         <f>'ICS2'!C113</f>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="B131" s="103">
         <f>'ICS2'!B111</f>
-        <v>2958465</v>
+        <v>46022</v>
       </c>
       <c r="C131" s="104">
         <f>'ICS2'!C111</f>
